--- a/output/hrv/female_HFD_HRV_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
+++ b/output/hrv/female_HFD_HRV_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\HeartAge\output\hrv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{557A0E35-20E5-4E45-9926-675F5BFC5166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C4816C-EB2C-485E-B3A3-1DCB6EED553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{AF359BBD-9497-474E-AFFC-742E27BC2796}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{1BD86B03-6AD7-4D34-9B26-35BDBF312F3D}"/>
   </bookViews>
   <sheets>
     <sheet name="female_HFD_HRV_ECG_calculated_n" sheetId="1" r:id="rId1"/>
@@ -641,6 +641,90 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Higuchi fractal dimension (HFD) for HRV fractal time series per each age range for all females </a:t>
+            </a:r>
+            <a:endParaRPr lang="uk-UA" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="uk-UA"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -653,13 +737,27 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -751,49 +849,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.9590000000000001</c:v>
+                  <c:v>1.9570000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.956</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.948</c:v>
+                  <c:v>1.9550000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.954</c:v>
+                  <c:v>1.96</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.954</c:v>
+                  <c:v>1.9650000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9339999999999999</c:v>
+                  <c:v>1.94</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.8959999999999999</c:v>
+                  <c:v>1.9179999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9079999999999999</c:v>
+                  <c:v>1.9259999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.9279999999999999</c:v>
+                  <c:v>1.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.929</c:v>
+                  <c:v>1.9330000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.909</c:v>
+                  <c:v>1.944</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.9179999999999999</c:v>
+                  <c:v>1.9019999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.8979999999999999</c:v>
+                  <c:v>1.9359999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.9910000000000001</c:v>
+                  <c:v>1.958</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.909</c:v>
+                  <c:v>1.9379999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -801,7 +899,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5EF8-475A-9656-6DE7679F8CFD}"/>
+              <c16:uniqueId val="{00000000-D246-4CAA-AC5C-DC87382AA529}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -814,11 +912,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="243715439"/>
-        <c:axId val="243720239"/>
+        <c:axId val="496129184"/>
+        <c:axId val="496133024"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="243715439"/>
+        <c:axId val="496129184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -861,7 +959,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="243720239"/>
+        <c:crossAx val="496133024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -869,7 +967,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="243720239"/>
+        <c:axId val="496133024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -889,6 +987,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>HFD</a:t>
+                </a:r>
+                <a:endParaRPr lang="uk-UA"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="uk-UA"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -920,7 +1074,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="243715439"/>
+        <c:crossAx val="496129184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1536,14 +1690,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542924</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>90487</xdr:rowOff>
     </xdr:to>
@@ -1552,7 +1706,7 @@
         <xdr:cNvPr id="2" name="Діаграма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DCEB85-9746-8C65-CE57-94A289F1B5F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{023427CC-36CF-AB6F-72EB-53202A4DD609}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1889,7 +2043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90B7558-76B0-479B-BE8C-61E25976B53D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{135DA3AC-7CAE-4B26-8D5C-8CD6B40107EF}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1898,7 +2052,7 @@
         <v>3</v>
       </c>
       <c r="B1">
-        <v>1.9590000000000001</v>
+        <v>1.9570000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1914,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1.948</v>
+        <v>1.9550000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1922,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1.954</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1930,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1.954</v>
+        <v>1.9650000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1938,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1.9339999999999999</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1946,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>1.8959999999999999</v>
+        <v>1.9179999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1954,7 +2108,7 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>1.9079999999999999</v>
+        <v>1.9259999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1962,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1.9279999999999999</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1970,7 +2124,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1.929</v>
+        <v>1.9330000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1978,7 +2132,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.909</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +2140,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>1.9179999999999999</v>
+        <v>1.9019999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1994,7 +2148,7 @@
         <v>8</v>
       </c>
       <c r="B13">
-        <v>1.8979999999999999</v>
+        <v>1.9359999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2156,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>1.9910000000000001</v>
+        <v>1.958</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2164,7 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>1.909</v>
+        <v>1.9379999999999999</v>
       </c>
     </row>
   </sheetData>
